--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F66B75E-E852-4CA4-8820-63503AD2A4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView xWindow="3590" yWindow="2010" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -271,29 +277,26 @@
     <t>UnitConfig.xlsx</t>
   </si>
   <si>
-    <t>DTDemo</t>
-  </si>
-  <si>
-    <t>DRDemo</t>
-  </si>
-  <si>
-    <t>Demo.xlsx</t>
-  </si>
-  <si>
     <t>c</t>
+  </si>
+  <si>
+    <t>DTGenAtom</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRGenAtom</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GenAtom.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,7 +316,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -321,7 +324,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,136 +335,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,182 +368,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -663,251 +377,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -915,80 +393,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="6" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="好" xfId="2" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1246,28 +682,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="29.08203125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="58.375" customWidth="1"/>
-    <col min="5" max="5" width="24.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="12.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="11.2166666666667" customWidth="1"/>
-    <col min="8" max="8" width="9.88333333333333" customWidth="1"/>
-    <col min="9" max="9" width="10.1083333333333" customWidth="1"/>
-    <col min="10" max="10" width="9.10833333333333" customWidth="1"/>
-    <col min="11" max="11" width="7.55" customWidth="1"/>
+    <col min="4" max="4" width="58.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.25" customWidth="1"/>
+    <col min="8" max="8" width="9.9140625" customWidth="1"/>
+    <col min="9" max="9" width="10.08203125" customWidth="1"/>
+    <col min="10" max="10" width="9.08203125" customWidth="1"/>
+    <col min="11" max="11" width="7.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1302,7 +738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1334,7 +770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1357,7 +793,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:11">
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1370,13 +806,11 @@
       <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:11">
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1389,13 +823,11 @@
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:11">
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>34</v>
       </c>
@@ -1408,13 +840,11 @@
       <c r="E6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:11">
+    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
@@ -1424,16 +854,14 @@
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:11">
+    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
@@ -1443,16 +871,14 @@
       <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:11">
+    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>43</v>
       </c>
@@ -1462,16 +888,14 @@
       <c r="D9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:11">
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>46</v>
       </c>
@@ -1484,13 +908,11 @@
       <c r="E10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>49</v>
       </c>
@@ -1510,7 +932,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>54</v>
       </c>
@@ -1530,7 +952,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +972,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>60</v>
       </c>
@@ -1570,7 +992,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>63</v>
       </c>
@@ -1580,7 +1002,7 @@
       <c r="D15" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G15" t="s">
@@ -1590,7 +1012,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>68</v>
       </c>
@@ -1607,7 +1029,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>71</v>
       </c>
@@ -1624,32 +1046,32 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" t="s">
         <v>74</v>
       </c>
-      <c r="C18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" t="s">
-        <v>77</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E15" r:id="rId1" display="OneConfig.xlsx"/>
-    <hyperlink ref="E7" r:id="rId2" display="Game/Sound@Sound.xlsx" tooltip="mailto:Sound@Sound.xlsx"/>
-    <hyperlink ref="E8" r:id="rId3" display="Game/UISound@Sound.xlsx"/>
-    <hyperlink ref="E9" r:id="rId1" display="Game/Music@Sound.xlsx"/>
+    <hyperlink ref="E15" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E7" r:id="rId2" tooltip="mailto:Sound@Sound.xlsx" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E9" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F66B75E-E852-4CA4-8820-63503AD2A4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E8DC1F-6A4E-467C-85DB-3E53726AFF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3590" yWindow="2010" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6380" yWindow="1050" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -289,6 +289,42 @@
   </si>
   <si>
     <t>GenAtom.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTSkill</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRSkill</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/Skill.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRSkillGraph</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTSkillGraph</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/SkillGraph.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTUnit</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRUnit</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/Unit.xlsx</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -688,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.08203125" customWidth="1"/>
@@ -1063,6 +1099,48 @@
         <v>74</v>
       </c>
     </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E8DC1F-6A4E-467C-85DB-3E53726AFF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABB15EB-C410-4F05-A7F0-95D4D218C730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="1050" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -1112,6 +1112,9 @@
       <c r="E19" s="6" t="s">
         <v>80</v>
       </c>
+      <c r="H19" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
@@ -1126,6 +1129,9 @@
       <c r="E20" s="6" t="s">
         <v>83</v>
       </c>
+      <c r="H20" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
@@ -1139,6 +1145,9 @@
       </c>
       <c r="E21" s="6" t="s">
         <v>86</v>
+      </c>
+      <c r="H21" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABB15EB-C410-4F05-A7F0-95D4D218C730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85094238-C85E-40BB-B8D2-A981646E5420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="90">
   <si>
     <t>##var</t>
   </si>
@@ -235,6 +235,7 @@
         <sz val="11"/>
         <color rgb="FF800080"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -246,6 +247,7 @@
         <sz val="11"/>
         <color rgb="FF800080"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -274,9 +276,6 @@
     <t>DRUnitConfig</t>
   </si>
   <si>
-    <t>UnitConfig.xlsx</t>
-  </si>
-  <si>
     <t>c</t>
   </si>
   <si>
@@ -316,15 +315,31 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>DTUnit</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRUnit</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Game/Unit.xlsx</t>
+    <t>Game/Hero.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTHero</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRHero</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTMonster</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRMonster</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/Monster.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/UnitConfig.xlsx</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -344,6 +359,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -352,6 +368,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -360,6 +377,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -367,12 +385,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -724,12 +744,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.08203125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="58.33203125" customWidth="1"/>
+    <col min="4" max="4" width="27.1640625" customWidth="1"/>
     <col min="5" max="5" width="24.33203125" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" customWidth="1"/>
     <col min="7" max="7" width="11.25" customWidth="1"/>
@@ -1075,8 +1095,8 @@
       <c r="D17" t="b">
         <v>1</v>
       </c>
-      <c r="E17" t="s">
-        <v>73</v>
+      <c r="E17" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="H17" t="s">
         <v>67</v>
@@ -1084,53 +1104,53 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="H18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>80</v>
-      </c>
       <c r="H19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="H20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
@@ -1144,10 +1164,27 @@
         <v>1</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="H21" t="s">
-        <v>74</v>
+      <c r="C22" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85094238-C85E-40BB-B8D2-A981646E5420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC59322B-AE7C-4682-991B-5150984AA756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
   <si>
     <t>##var</t>
   </si>
@@ -340,6 +340,22 @@
   </si>
   <si>
     <t>Game/UnitConfig.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/GameAI.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTGameAI</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRGameAI</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -744,13 +760,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.08203125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="27.1640625" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" customWidth="1"/>
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="9.9140625" customWidth="1"/>
@@ -1185,6 +1201,23 @@
       </c>
       <c r="H22" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC59322B-AE7C-4682-991B-5150984AA756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8EA612-4CE6-4145-8248-D1A537B671B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8EA612-4CE6-4145-8248-D1A537B671B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92CB399-1FAC-4765-8121-8B63332BBCF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6010" yWindow="2750" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
@@ -270,92 +270,110 @@
     <t>AIConfig.xlsx</t>
   </si>
   <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>DTGenAtom</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRGenAtom</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GenAtom.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTSkill</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRSkill</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/Skill.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRSkillGraph</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTSkillGraph</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/SkillGraph.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/Hero.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTHero</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRHero</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTMonster</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRMonster</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/Monster.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/GameAI.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTGameAI</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRGameAI</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTUnitAttribute</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRUnitAttribute</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRUnitConfig</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitConfig@Game/UnitConfig.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>DTUnitConfig</t>
-  </si>
-  <si>
-    <t>DRUnitConfig</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>DTGenAtom</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRGenAtom</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>GenAtom.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DTSkill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRSkill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Game/Skill.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRSkillGraph</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DTSkillGraph</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Game/SkillGraph.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Game/Hero.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DTHero</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRHero</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DTMonster</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRMonster</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Game/Monster.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Game/UnitConfig.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Game/GameAI.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DTGameAI</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRGameAI</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConfigId+Level</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeroAttribute@Game/UnitConfig.xlsx,MonsterAttribute@Game/UnitConfig.xlsx</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -760,13 +778,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.08203125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="27.1640625" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.9140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" customWidth="1"/>
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="9.9140625" customWidth="1"/>
@@ -1102,17 +1120,17 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
+      <c r="B17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s">
         <v>67</v>
@@ -1120,104 +1138,124 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>97</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="H18" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>90</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92CB399-1FAC-4765-8121-8B63332BBCF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6ACE64-CD49-4D18-A9E4-BAA6149AB020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6010" yWindow="2750" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -361,10 +361,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>UnitConfig@Game/UnitConfig.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>DTUnitConfig</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -373,7 +369,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>HeroAttribute@Game/UnitConfig.xlsx,MonsterAttribute@Game/UnitConfig.xlsx</t>
+    <t>Game/UnitConfig.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/UnitConfigAttr.xlsx</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -784,8 +784,8 @@
     <col min="2" max="2" width="29.08203125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="27.1640625" customWidth="1"/>
-    <col min="5" max="5" width="64.9140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="29.4140625" customWidth="1"/>
+    <col min="6" max="6" width="14.08203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="9.9140625" customWidth="1"/>
     <col min="9" max="9" width="10.08203125" customWidth="1"/>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>93</v>
@@ -1130,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H17" t="s">
         <v>67</v>
@@ -1150,7 +1150,7 @@
         <v>97</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s">
         <v>67</v>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6ACE64-CD49-4D18-A9E4-BAA6149AB020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B23686-15C3-4EC7-9D89-FD6E20C7CBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="29.08203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1194,75 +1194,100 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>DTSkillCardRule</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>DRSkillCardRule</t>
         </is>
       </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>Game/SkillCardRule.xlsx</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>DTBattleCardConfig</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>DRBattleCardConfig</t>
         </is>
       </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>Game/BattleCardConfig.xlsx</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>DTRelic</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>DRRelic</t>
         </is>
       </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>Game/Relic.xlsx</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DTSkillAttribute</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DRSkillAttribute</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Game/SkillAttribute.xlsx</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>c</t>
         </is>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926E97C7-00B5-43B7-90F7-A53D6F11B249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D705E8-39C4-4843-9DA8-AE862CAE3519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5920" yWindow="2390" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="115">
   <si>
     <t>##var</t>
   </si>
@@ -367,6 +367,10 @@
   </si>
   <si>
     <t>c,e</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id+Level</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -427,6 +431,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -471,7 +476,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -497,6 +502,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1318,6 +1324,9 @@
       <c r="E28" t="s">
         <v>107</v>
       </c>
+      <c r="F28" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="H28" t="s">
         <v>80</v>
       </c>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D705E8-39C4-4843-9DA8-AE862CAE3519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41352CFC-525C-486E-B6CE-0BE5F835F8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5920" yWindow="2390" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -250,9 +250,6 @@
     <t>Game/UnitConfigAttr.xlsx</t>
   </si>
   <si>
-    <t>ConfigId+Level</t>
-  </si>
-  <si>
     <t>DTGenAtom</t>
   </si>
   <si>
@@ -371,6 +368,10 @@
   </si>
   <si>
     <t>Id+Level</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConfigId+Level+SubLevel</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -787,7 +788,7 @@
     <col min="3" max="3" width="18" style="7" customWidth="1"/>
     <col min="4" max="4" width="27.1640625" style="7" customWidth="1"/>
     <col min="5" max="5" width="29.4140625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="14.08203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" style="7" customWidth="1"/>
     <col min="7" max="7" width="11.25" style="7" customWidth="1"/>
     <col min="8" max="8" width="9.9140625" style="7" customWidth="1"/>
     <col min="9" max="9" width="10.08203125" style="7" customWidth="1"/>
@@ -921,7 +922,7 @@
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>34</v>
@@ -933,7 +934,7 @@
         <v>35</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -984,7 +985,7 @@
         <v>44</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1152,7 +1153,7 @@
         <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="H18" t="s">
         <v>66</v>
@@ -1160,195 +1161,195 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="H19" t="s">
         <v>79</v>
-      </c>
-      <c r="H19" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="H20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="H21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="H22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="H23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="H24" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
         <v>96</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
         <v>97</v>
       </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>98</v>
-      </c>
       <c r="H25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
         <v>99</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
         <v>100</v>
       </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>101</v>
-      </c>
       <c r="H26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" t="s">
         <v>102</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
         <v>103</v>
       </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>104</v>
-      </c>
       <c r="H27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
         <v>105</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
         <v>106</v>
       </c>
-      <c r="D28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>107</v>
-      </c>
       <c r="F28" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="G29" t="s">
         <v>65</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41352CFC-525C-486E-B6CE-0BE5F835F8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECB7202-A1F2-40D5-85F9-D8029A23EB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="2730" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="118">
   <si>
     <t>##var</t>
   </si>
@@ -372,6 +372,18 @@
   </si>
   <si>
     <t>ConfigId+Level+SubLevel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTItems</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRItems</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/Items.xlsx</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -781,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.08203125" style="7" customWidth="1"/>
@@ -1352,6 +1364,24 @@
         <v>112</v>
       </c>
     </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G30"/>
+      <c r="H30" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -1360,6 +1390,7 @@
     <hyperlink ref="E9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="E15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="E29" r:id="rId5" display="OneConfig.xlsx" xr:uid="{69425F25-CF7D-487F-85EF-3BE696BCC05B}"/>
+    <hyperlink ref="E30" r:id="rId6" display="OneConfig.xlsx" xr:uid="{1A196BF1-98B7-45AF-B927-F72C345277F7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECB7202-A1F2-40D5-85F9-D8029A23EB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6A8C4F-45AA-4FE2-805F-6D995EB74AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="2730" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="121">
   <si>
     <t>##var</t>
   </si>
@@ -384,6 +384,18 @@
   </si>
   <si>
     <t>Game/Items.xlsx</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTStages</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRStages</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/Stages.xlsx</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -793,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.08203125" style="7" customWidth="1"/>
@@ -1382,6 +1394,24 @@
         <v>112</v>
       </c>
     </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G31"/>
+      <c r="H31" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -1391,6 +1421,7 @@
     <hyperlink ref="E15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="E29" r:id="rId5" display="OneConfig.xlsx" xr:uid="{69425F25-CF7D-487F-85EF-3BE696BCC05B}"/>
     <hyperlink ref="E30" r:id="rId6" display="OneConfig.xlsx" xr:uid="{1A196BF1-98B7-45AF-B927-F72C345277F7}"/>
+    <hyperlink ref="E31" r:id="rId7" display="OneConfig.xlsx" xr:uid="{F6272B47-86E5-48E6-8E18-B1BC761CF723}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6A8C4F-45AA-4FE2-805F-6D995EB74AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D04580C-2E1E-4BA1-8C14-0823A1AB0DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2210" yWindow="2070" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="124">
   <si>
     <t>##var</t>
   </si>
@@ -396,6 +396,18 @@
   </si>
   <si>
     <t>Game/Stages.xlsx</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTDrops</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRDrops</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game/Drops.xlsx</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -805,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.08203125" style="7" customWidth="1"/>
@@ -1412,6 +1424,24 @@
         <v>112</v>
       </c>
     </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G32"/>
+      <c r="H32" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -1422,6 +1452,7 @@
     <hyperlink ref="E29" r:id="rId5" display="OneConfig.xlsx" xr:uid="{69425F25-CF7D-487F-85EF-3BE696BCC05B}"/>
     <hyperlink ref="E30" r:id="rId6" display="OneConfig.xlsx" xr:uid="{1A196BF1-98B7-45AF-B927-F72C345277F7}"/>
     <hyperlink ref="E31" r:id="rId7" display="OneConfig.xlsx" xr:uid="{F6272B47-86E5-48E6-8E18-B1BC761CF723}"/>
+    <hyperlink ref="E32" r:id="rId8" display="OneConfig.xlsx" xr:uid="{24387CD4-CECF-4F0F-AFCC-9B02DFBDD6F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
